--- a/market_prices.xlsx
+++ b/market_prices.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Market Prices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Market Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,43 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000000FF"/>
+        <bgColor rgb="000000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00800080"/>
+        <bgColor rgb="00800080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+        <bgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +76,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,192 +461,1162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tier 5, Enchantment 1, Quality Normal</t>
+          <t>Caerleon</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Lymhurst</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Martlock</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Thetford</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>Fort Sterling</t>
+        </is>
+      </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>Bridgewatch</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Expert's Feyscale Robe</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>948,717</t>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Enchantment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Enchantment</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Enchantment</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Enchantment</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Enchantment</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Enchantment</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Expert's Lightcaller</t>
+          <t>Master's</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>726,254</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1221148</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Master's</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1221148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Expert's Mistwalker Jacket</t>
+          <t>twalker Jacket</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>672,179</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1105739</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>twalker Jacket</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1105739</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Expert's Fiend Robe</t>
+          <t>Master's Royal Robe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>59,236</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1104096</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Master's Royal Robe</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1104096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Expert's Cultist Robe</t>
+          <t>Master's Royal Robe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>58,867</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1089309</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Master's Royal Robe</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>1089309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Expert's Forge Hammers</t>
+          <t>Master's Royal Armor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58,232</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>329221</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Master's Royal Armor</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>329221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Expert's Caitiff Shield</t>
+          <t>Master's Fort Sterling Cape</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>57,730</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>329221</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Master's Fort Sterling Cape</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>329221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Expert's Rampant Staff</t>
+          <t>Master's Morgana Cape</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21,904</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>327750</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Master's Morgana Cape</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>327750</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Expert's Trinity Spear</t>
+          <t>Master's Avalonian Cape</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,904</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>320346</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Master's Avalonian Cape</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>320346</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Expert's Scholar Robe</t>
+          <t>Master's Mistwalker Hood</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,900</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220880</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Master's Mistwalker Hood</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>220880</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Expert's Glacial Staff</t>
+          <t>Master's Occult Staff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21,900</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>216864</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Master's Occult Staff</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>216864</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Tier 8, Enchantment 4, Quality Normal</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Master's Demonfang</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>216080</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Master's Demonfang</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>216080</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Elder's Great Frost Staff</t>
+          <t>Master's Double Bladed Stat</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>52,801,510</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>213564</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Master's Double Bladed Stat</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>213564</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vendetta's Wrath</t>
+          <t>Master's Deathgivers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48,502,626</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167552</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Master's Deathgivers</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>167552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elder's Glaive</t>
+          <t>Master's Hoarfrost Staff</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50,091,344</t>
-        </is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>166440</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Master's Hoarfrost Staff</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>166440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Master's Morning Star</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>160640</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Master's Morning Star</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>160640</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Master's Brimstone Staff</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>160160</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Master's Brimstone Staff</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>160160</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Master's Heron Spear</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>127255</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Master's Heron Spear</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>127255</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Master's</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>127020</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Master's</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>127020</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Master's Broadsword</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>126500</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Master's Broadsword</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>126500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Master's Avalonian Cape</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>125948</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Master's Avalonian Cape</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>125948</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="S1:W1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="Y1:AC1"/>
+    <mergeCell ref="M1:Q1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>